--- a/emails_output/emails.xlsx
+++ b/emails_output/emails.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>UID</t>
   </si>
@@ -25,294 +25,20 @@
     <t>Attachments</t>
   </si>
   <si>
-    <t>9896</t>
-  </si>
-  <si>
-    <t>9897</t>
-  </si>
-  <si>
-    <t>9898</t>
-  </si>
-  <si>
-    <t>9899</t>
-  </si>
-  <si>
-    <t>9900</t>
-  </si>
-  <si>
-    <t>9901</t>
-  </si>
-  <si>
-    <t>9902</t>
-  </si>
-  <si>
-    <t>9903</t>
-  </si>
-  <si>
-    <t>9904</t>
-  </si>
-  <si>
-    <t>9905</t>
-  </si>
-  <si>
-    <t>MongoDB &lt;mongodbteam@messages.mongodb.com&gt;
-To view this email as a web page, go to the following address: https://info.mongodb.com/index.php/email/emailWebview?mkt_tok=MTQ5LUNCSi0xMzYAAAGguYwlXakzx6ur_uwPwzmDXyUfclttn3FumR7HAdDtj67TjhbrB9uKZiNLA1s_dtRBR4mcLKN0YpF5GykRlcPBHIIffgL8MALhhnyZjgEGBqkxwg _x000D_
+    <t>12</t>
+  </si>
+  <si>
+    <t>---------- Forwarded message ---------_x000D_
+From: yessine tony &lt;yessinetony@gmail.com&gt;_x000D_
+Date: Mon, 6 Apr 2026 at 10:22_x000D_
+Subject: nigga_x000D_
+To: Yessineht@gmail.com &lt;Yessineht@gmail.com&gt;_x000D_
 _x000D_
 _x000D_
-Bonjour Yessine,_x000D_
-_x000D_
-_x000D_
-Que vous souhaitiez développer vos compétences ou mieux comprendre tout le potentiel des solutions MongoDB, notre Programme de Certification vous accompagne avec une certification officielle à la clé._x000D_
-_x000D_
-Conçue par les experts MongoDB, cette formation vous permettra d’approfondir vos connaissances, de développer vos compétences et de valoriser votre expertise._x000D_
-_x000D_
-En vous inscrivant, vous bénéficierez de :_x000D_
-_x000D_
-_x000D_
-	- 9 sessions en direct animées par des experts MongoDB_x000D_
-	- Un contenu exclusif, avec des cas d’usage avancés_x000D_
-	- Un examen de certification officiel gratuit_x000D_
-_x000D_
-_x000D_
-_x000D_
-Que vous soyez développeur, architecte ou responsable data, ce programme vous aidera à mieux exploiter les opportunités offertes par les architectures de données modernes MongoDB._x000D_
-Inscrivez-vous  &lt;https://em.mongodb.com/MTQ5LUNCSi0xMzYAAAGguYwlXTuCIKP6_LoBDLdFIsmZKyH45iQ6nDGf-UFAtSTG3VC72eDm9R1cwzlFDJWZw66Qw1Q=&gt;_x000D_
-Think Big. Go Far,_x000D_
-The MongoDB Team_x000D_
-_x000D_
-This email was sent to yessineht@gmail.com. If you no longer wish to receive these emails you may unsubscribe here: https://info.mongodb.com/UnsubscribePage.html?mkt_unsubscribe=1&amp;mkt_tok=MTQ5LUNCSi0xMzYAAAGguYwlXakzx6ur_uwPwzmDXyUfclttn3FumR7HAdDtj67TjhbrB9uKZiNLA1s_dtRBR4mcLKN0YpF5GykRlcPBHIIffgL8MALhhnyZjgEGBqkxwg.</t>
-  </si>
-  <si>
-    <t>AliExpress &lt;promotion@aliexpress.com&gt;
-         #outlook a { padding:0; } body { margin:0;padding:0;-webkit-text-size-adjust:100%;-ms-text-size-adjust:100%; } table, td { border-collapse:collapse;mso-table-lspace:0pt;mso-table-rspace:0pt; } img { border:0;height:auto;line-height:100%; outline:none;text-decoration:none;-ms-interpolation-mode:bicubic; } p { display:block;margin:13px 0; }      96      .mj-outlook-group-fix { width:100% !important; }     x @import url(https://fonts.googleapis.com/css?family=Open+Sans:300,400,500,700);      @import url(https://fonts.googleapis.com/css?family=Open+Sans:300,400,500,700);        @import url(https://fonts.googleapis.com/css?family=Roboto:300,400,500,700);        @import url(https://fonts.googleapis.com/css?family=Roboto:300,400,500,700);        @import url(https://fonts.googleapis.com/css?family=Roboto:300,400,500,700);        @import url(https://fonts.googleapis.com/css?family=Open+Sans:300,400,500,700);      @media screen and (min-width: 480px) { .list-one-two-left-item-card .list-one-two-product-name { font-size: 18px !important; line-height: 22px !important; } .list-one-two-left-item-card .list-one-two-item-card-text { padding: 16px 24px 0px; } .list-one-two-left-item-card .list-one-two-price { padding-top: 1px !important; font-size: 24px !important; line-height: 32px !important; } .list-one-two-left-item-card .list-one-two-split { height: 16px !important; font-size: 15px !important; line-height: 15px !important; } .list-one-two-left-item-card .list-one-two-ori-price { font-size: 15px !important; line-height: 19px !important; } .list-one-two-left-item-card .list-one-two-product-price-off { font-size: 15px !important; line-height: 19px !important; } .list-one-two-right-item-card .list-one-two-product-name { font-size: 15px !important; line-height: 19px !important; } .list-one-two-right-item-card .list-one-two-price { font-size: 20px !important; line-height: 24px !important; } .list-one-two-right-item-card .list-one-two-ori-price { font-size: 15px !important; line-height: 19px !important; } .list-one-two-module-title { font-size: 20px !important; font-weight: 700 !important; line-height: 24px !important; } .free-shipping-icon { width: 20px !important; height: 20px !important; } .free-shipping-text { font-weight: 400 !important; font-size: 15px !important; line-height: 19px !important; color: #009966 !important; } .logistics-timeliness-icon { width: 14px !important; height: 14px !important; } .logistics-timeliness-text { font-weight: 400 !important; font-size: 15px !important; line-height: 19px !important; color: #009966 !important; } .reverse-return-text { font-size: 15px !important; line-height: 19px !important; color: #009966 !important; } .selling-point-text { font-size: 12px !important; line-height: 16px !important; } .sales-text { font-size: 15px !important; line-height: 19px !important; color: #191919 !important; } .product-rating-icon { width: 15px !important; height: 15px !important; } .product-rating-text { font-size: 15px !important; line-height: 19px !important; color: #191919 !important; } @media screen and (min-width: 480px) { .EDM-COLUMNS-THREE-discount div { margin-bottom: 0px !important; } } .bottomNavigation-v1-title div { font-size: 20px !important; line-height: 24px !important; font-weight: 700 !important; } }                                         Découvrez vos offres de rêves &amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;                                                                                        Redécouvrez votre chez vous              2,96€ 5,91€ | -50%         &amp;nbsp;           131,20€ 262,40€          .              141,55€ 410,97€          &amp;nbsp;                   &amp;nbsp;      Explorer plus      &amp;nbsp;                 .          .     .          .      -67%  321,49€      .          .      -32%  32,81€      .          .      -66%  162,54€      .    .     .          .      .  69,23€      .          .      -50%  169,36€      .          .      -50%  60,80€      .    .     .          .      .  26,92€      .          .      -53%  63,89€      .          .      -50%  21,90€      .    .     .          .      -40%  10,64€      .          .      -50%  21,82€      .          .      -65%  1,25€      .    .     .          .      .  32,29€      .          .      -72%  19,48€      .          .      -50%  3,22€      .    .     .          .      -50%  141,31€      .          .      -66%  44,23€      .          .      -30%  25,08€      .    .     .          .      -67%  122,45€      .          .      -50%  89,46€      .          .      -50%  12,38€      .    .      .                  &amp;nbsp;      Voir plus      &amp;nbsp;                  Populaire         Art  Articles ménagers  Cuisine         Outils  Amélioration de l'habitat  Éclairage d'intérieur                    Les prix, offres et disponibilités affichés dans cet email sont valables à l'heure de l'envoi et peuvent changer. Veuillez noter que les frais d'envoi ne sont pas inclus. Rendez-vous sur la page de l'article pour voir les informations à jour.                  Téléchargez l'application pour profiter d'offres exclusives                                                 Cet email a été envoyé à yessi****@gmail.com     Vous recevez cet email car vous êtes un membre de www.AliExpress.com.    Pour ne plus recevoir nos emails promotionnels, Cliquez ici    Lisez notre Politique de confidentialité et conditions d'utilisation si vous avez des questions.    Centre de service clientèle AliExpress    Alibaba.com Singapore E-Commerce Private Limited,     c/o 26/F Tower One, Times Square, 1 Matheson Street, Causeway Bay, Hong Kong</t>
-  </si>
-  <si>
-    <t>sirine &lt;sirine@lunflow.com&gt;
-Bonsoir , ok merci_x000D_
-_x000D_
-On 3/23/2026 7:56 PM, Yessine Ht wrote:_x000D_
-&gt; Bonjour,_x000D_
-&gt;_x000D_
-&gt; Je vous envoie ce mail pour vous informer que nous avons essayé de _x000D_
-&gt; contacter notre encadrant académique par téléphone, mais nous n’avons _x000D_
-&gt; pas réussi à le joindre.</t>
-  </si>
-  <si>
-    <t>sirine &lt;sirine@lunflow.com&gt;
-ok_x000D_
-_x000D_
-On 3/23/2026 8:03 PM, Yessine Ht wrote:_x000D_
-&gt; Bonsoir_x000D_
-&gt;_x000D_
-&gt; Je m’excuse pour le message précédent. Notre encadrant académique _x000D_
-&gt; vient de nous rappeler et a confirmé qu’il est d’accord pour la _x000D_
-&gt; réunion. Il sera disponible entre 10h et 11h._x000D_
-&gt;_x000D_
-&gt; On Mon, Mar 23, 2026, 19:58 sirine &lt;sirine@lunflow.com&gt; wrote:_x000D_
-&gt;_x000D_
-&gt;     Bonsoir , ok merci_x000D_
-&gt;_x000D_
-&gt;     On 3/23/2026 7:56 PM, Yessine Ht wrote:_x000D_
-&gt;     &gt; Bonjour,_x000D_
-&gt;     &gt;_x000D_
-&gt;     &gt; Je vous envoie ce mail pour vous informer que nous avons essayé de_x000D_
-&gt;     &gt; contacter notre encadrant académique par téléphone, mais nous_x000D_
-&gt;     n’avons_x000D_
-&gt;     &gt; pas réussi à le joindre._x000D_
-&gt;</t>
-  </si>
-  <si>
-    <t>daily.dev &lt;informer@daily.dev&gt;
-We picked posts from your topics based on what the community found useful  _x000D_
-_x000D_
-*******_x000D_
-For you_x000D_
-*******_x000D_
-_x000D_
-​Mar 24, 2026_x000D_
-_x000D_
-Logo ( https://app.daily.dev/ )_x000D_
-_x000D_
-daily.dev ( https://app.daily.dev/posts/kaAWQy79n?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
-_x000D_
-How we built a Linear coding agent: the hard parts ( https://app.daily.dev/posts/kaAWQy79n?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
----------------------------------------------------------------------------------------------------------------------------------------------------------_x000D_
-_x000D_
-Read_x000D_
-article → ( https://app.daily.dev/posts/kaAWQy79n?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
-_x000D_
-Josh W Comeau ( https://app.daily.dev/posts/4AgbREn59?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
-_x000D_
-Sneaky Header Blocker Trick • Josh W. Comeau ( https://app.daily.dev/posts/4AgbREn59?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
------------------------------------------------------------------------------------------------------------------------------------------------------_x000D_
-_x000D_
-Read_x000D_
-article → ( https://app.daily.dev/posts/4AgbREn59?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
-_x000D_
-TkDodo ( https://app.daily.dev/posts/wSju3VMXu?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
-_x000D_
-Test IDs are an a11y smell ( https://app.daily.dev/posts/wSju3VMXu?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
----------------------------------------------------------------------------------------------------------------------------------_x000D_
-_x000D_
-Read_x000D_
-article → ( https://app.daily.dev/posts/wSju3VMXu?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
-_x000D_
-Tech World With Milan ( https://app.daily.dev/posts/V90BEtMZY?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
-_x000D_
-You're Not Paid to Write Code ( https://app.daily.dev/posts/V90BEtMZY?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
-------------------------------------------------------------------------------------------------------------------------------------_x000D_
-_x000D_
-Read_x000D_
-article → ( https://app.daily.dev/posts/V90BEtMZY?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
-_x000D_
-Engineering Enablement ( https://app.daily.dev/posts/MCzNO6zN8?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
-_x000D_
-AI productivity gains are 10%, not 10x ( https://app.daily.dev/posts/MCzNO6zN8?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
----------------------------------------------------------------------------------------------------------------------------------------------_x000D_
-_x000D_
-Read_x000D_
-article → ( https://app.daily.dev/posts/MCzNO6zN8?utm_source=notification&amp;utm_medium=email&amp;utm_campaign=digest )_x000D_
-_x000D_
-Fast-track your growth. Upgrade to plus ( https://app.daily.dev/plus )_x000D_
-_x000D_
-Try daily.dev on mobile (if you haven’t yet)_x000D_
-_x000D_
-( https://apps.apple.com/app/daily-dev/id6740634400 )_x000D_
-daily.dev for iOS ( https://apps.apple.com/app/daily-dev/id6740634400 )_x000D_
-_x000D_
-( https://play.google.com/store/apps/details?id=dev.daily )_x000D_
-daily.dev for Android ( https://play.google.com/store/apps/details?id=dev.daily )_x000D_
-_x000D_
-Explore ( https://app.daily.dev/posts )   |   Discussions ( https://app.daily.dev/discussed )   |   Tags ( https://app.daily.dev/tags )   |   Sources ( https://app.daily.dev/sources )   |   Leaderboard ( https://app.daily.dev/users )_x000D_
-_x000D_
-X ( https://twitter.com/dailydotdev ) Yt ( https://www.youtube.com/c/dailydev )_x000D_
-Inst ( https://www.instagram.com/dailydotdev/ ) Tt ( https://www.tiktok.com/@dailydotdev )_x000D_
-GitHub ( https://github.com/dailydotdev/daily )_x000D_
-This email was intended for Yessine Ht (yessineht@gmail.com)_x000D_
-Settings notifications ( https://app.daily.dev/account/notifications ), account details ( https://app.daily.dev/account/profile ) or unsubscribe ( https://track.customer.io/manage_subscription_preferences/RLnCCQUAAZ0eOxYRP82OWI9PHu-BzQ== ) _x000D_
-_x000D_
-( https://app.daily.dev )Daily Dev Ltd., 9 Derech HaTikva Ganei Tikva, Israel_x000D_
-5591252</t>
-  </si>
-  <si>
-    <t>Sirine Mseddi &lt;sirine@lunflow.com&gt;
-Stage PFE | Meeting-Join | Microsoft Teams _x000D_
-&lt;https://teams.live.com/meet/9380450426691?p=QDodeW6TqEQcBOCwP6&gt;_x000D_
-_x000D_
--- _x000D_
-Sirine Mseddi_x000D_
-Tech Lead – Lunar TC_x000D_
-📞 93255255 | ✉️sirine@lunflow.com_x000D_
-🌐www.lunflow.com</t>
-  </si>
-  <si>
-    <t>YouTube &lt;no-reply@youtube.com&gt;
-_x000D_
-YOU'VE BEEN INVITED TO ACCESS THE CHANNEL STORY_RUSH AS A MANAGER_x000D_
-_x000D_
-_x000D_
-Managers can view everything, manage permissions, go live, and create, edit  _x000D_
-and delete content._x000D_
-_x000D_
-Accept this invitation to gain access to Story_Rush._x000D_
-_x000D_
-_x000D_
-Accept invitation  _x000D_
-&lt;https://studio.youtube.com/?channel_id=UCrkEbrnyPJB9JXXoN7fQKVA&amp;invitation_id=HwpE5mqJ99eSWkKCOYUtraLhDPc&amp;token=lYYcY15JZmDM1Ahh3FKZFQ&amp;invitee=yessineht@gmail.com&gt;_x000D_
-By accepting this invitation, people who have access to this channel will  _x000D_
-be able to see your name, avatar, email address and the changes that you  _x000D_
-make to the channel._x000D_
-_x000D_
-When you're logged in to YouTube as this channel:_x000D_
-_x000D_
-* Your private activity is attributed to your personal account (for  _x000D_
-example, searching and watching videos)_x000D_
-* Your public activity is attributed to the channel (for example, uploading  _x000D_
-videos and commenting)_x000D_
-_x000D_
-Learn more  _x000D_
-&lt;https://c.gle/ADMV5J-kf6YJqkPKq_CFEuqMpI7sKkGAqXO687E6BQXH_nJcnVRUvsPRWN2gt1mJXCS6m74q1P1Akk6tlzhDE2BCOJYFhj9gTZCAMfPr7B1-OFXmxh8trxzKfkp4qjxIJgPLDBWBy_HpbxBMR66BvTG6cjf2R-jNDLw8WxLdzd0Z1_4gwuhA&gt;_x000D_
-_x000D_
-This invitation expires in 30 days._x000D_
-_x000D_
-Yours sincerely,_x000D_
-The YouTube team_x000D_
-_x000D_
-Subscribe to the YouTube Creators channel  _x000D_
-&lt;https://c.gle/ADMV5J-fpGZBianbqhxepfrP2rwuJ5rwx4it3Vh38CpayXfRf-bzSk47C0OjrNwrTveFc5AjQqwbN25G1YGKLToSlzS9nM_pgHZ-zgUZXbk1FRoBmMu06zPSRnSDGxUrNsYxsl8qjUQZcCGgy9yZ4mLfkr6RM1O6WHw_PPVYC2Y&gt;_x000D_
-Follow YouTube Creators on Instagram  _x000D_
-&lt;https://c.gle/ADMV5J8nCsg-eUK7B5ag_dpVRQ96BFJq4zuwo8wN69xhFJDTWoEkuCQJtnp8aqiEEJHFZq7Fh1yZfthrzp0AaN_C_cYgwk5GtQSJzT951xc2O8OR08dK0nMMd5j0uFKbXE_LcC3vUF9_O2q_MIY3Or7SkKCbjvPvHtBxekvT6Bvn&gt;_x000D_
-Follow YouTube Creators on X  _x000D_
-&lt;https://c.gle/ADMV5J8rF8NfZGrylz_6zz5mdUpJA_Xc2dP9sMcbg_1q7wLgnvfs0y6nBgqPbY6MyGrs0U-sBJkCOMdOS9vI5ejPXPSqD0nqSENoRly8beREfRSJBawFCl-DYi4kYmhnSBzeBH9gxjb-2HybEhgil8pk&gt;_x000D_
-_x000D_
-Help Centre  _x000D_
-&lt;https://c.gle/ADMV5J_g4L1laXaLZwNXbIPGu1vlKEPI-7-6PkZqL9v3g-MktiCFUgJI4TkmTz1HZCVDkwPv-7622htne3NSaGh48Ohieaneoq9ZODM92RWQJF_0bOY-gb8tRxMs1G-bn5pfFtplSvXMg79ZExaZsHFP-3opKQ&gt;_x000D_
-_x000D_
-Email options  _x000D_
-&lt;https://c.gle/ADMV5J9TrBGQp8i39ZVyWjwU8SZOe_9KmzIaZty5OdJ_I7dpmdJUTQwfJLdMMhd4XAwI4HwoYnuwv1y_7rSEC35HlmGQnfCgR92YjqK-5isf2Yj5s1TO1hkFRVtbzKscs0u_FbDN_0p6Qewu0D6_jS5tD6NL3dzYmEwqVwxzpEVhDqxXz2-4zq0_XeEEO84Hp5w58-hNlTYnx5wvrmFYwQ9qD49sJ1nOFOY9&gt;_x000D_
-_x000D_
-You've received this email because someone shared a channel with you from  _x000D_
-YouTube Studio._x000D_
-_x000D_
-_x000D_
-(c) 2026 Google LLC d/b/a YouTube, 901 Cherry Ave, San Bruno, CA 94066</t>
-  </si>
-  <si>
-    <t>Ollama &lt;hello@ollama.com&gt;
-_x000D_
- _x000D_
-_x000D_
-https://ollama.com/upgrade?plan=pro&amp;interval=year_x000D_
-_x000D_
-_x000D_
-New Pro annual plan_x000D_
-_x000D_
-Ollama's Pro plan now has an annual option. For $200/year, you get 2 months free compared to the monthly plan._x000D_
- _x000D_
-_x000D_
-Upgrade to Pro annual [https://ollama.com/upgrade?plan=pro&amp;interval=year]_x000D_
-_x000D_
- _x000D_
-Ollama Pro and Max give you fast, reliable access to the newest open models like Nemotron-3-Super, Kimi-K2.5, MiniMax-M2.7, GLM-5,_x000D_
-and GPT-OSS with built-in support for OpenClaw, Claude Code, and more._x000D_
- _x000D_
-If you have any feedback, reply directly to this email or join Ollama's Discord channel [https://discord.gg/ollama]._x000D_
- _x000D_
-❤️ Ollama_x000D_
- _x000D_
-You are receiving this email because you opted-in to receive updates from Ollama_x000D_
-Ollama, 744 High Street, Palo Alto, CA 94301_x000D_
-Unsubscribe [https://app.loops.so/unsubscribe/cmn4mnvbr02dq016e4eahcr8p/6cd311c7e32c2bb4c253d1cbd931c8f99cb8a4c95896e6a576bc64952599b744f045a33af8ba5e48e238fd61cdd345be5ff5c45a699e1f80516c34b2]</t>
-  </si>
-  <si>
-    <t>AliExpress &lt;ae-best-message-notice08@newarrival.aliexpress.com&gt;
-         #outlook a { padding:0; } body { margin:0;padding:0;-webkit-text-size-adjust:100%;-ms-text-size-adjust:100%; } table, td { border-collapse:collapse;mso-table-lspace:0pt;mso-table-rspace:0pt; } img { border:0;height:auto;line-height:100%; outline:none;text-decoration:none;-ms-interpolation-mode:bicubic; } p { display:block;margin:13px 0; }      96      .mj-outlook-group-fix { width:100% !important; }     x @import url(https://fonts.googleapis.com/css?family=Open+Sans:300,400,500,700);      @import url(https://fonts.googleapis.com/css?family=Roboto:300,400,500,700);        @import url(https://fonts.googleapis.com/css?family=Roboto:300,400,500,700);        @import url(https://fonts.googleapis.com/css?family=Roboto:300,400,500,700);        @import url(https://fonts.googleapis.com/css?family=Roboto:300,400,500,700);      @media screen and (min-width: 480px) { @media screen and (min-width: 480px) { .EDM-COLUMNS-THREE-discount div { margin-bottom: 0px !important; } } }                                         Ces trouvailles vont vous plaire &amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;&amp;nbsp;&amp;zwnj;                                                                                              .               .          -50%  .   18,92€        .            -50%  .   10,37€          .              -49%  .   28,18€                .                  &amp;nbsp;      Voir les offres      &amp;nbsp;                 .               .      -50%  69,17€      .          .      -50%  3,72€      .          .      -50%  20,09€       .           .      -17%  86,49€      .          .      -34%  16,90€      .          .      -50%  20,51€       .           .      -40%  69,85€      .          .      -50%  17,13€      .          .      -20%  75,63€       .           .      .  5,84€      .          .      -60%  0,96€      .          .      -17%  2,94€       .           .      -11%  68,92€      .          .      -50%  3,08€      .          .      -47%  28,29€       .           .      -65%  17,54€      .          .      -24%  73,58€      .          .      -50%  1,37€       .           .      -51%  15,83€      .          .      -51%  8,03€      .          .      -49%  2,20€      .       Voir plus         .                 &amp;nbsp;        Catégories populaires    .        Maison  .   Électronique  .   Téléphones      Beauté  .   Sport  .   Jouets      &amp;nbsp;                 Les prix, offres et disponibilités affichés dans cet email sont valables à l'heure de l'envoi et peuvent changer. Veuillez noter que les frais d'envoi ne sont pas inclus. Rendez-vous sur la page de l'article pour voir les informations à jour.                  Téléchargez l'application pour profiter d'offres exclusives                                                 Cet email a été envoyé à yessi****@gmail.com     Vous recevez cet email car vous êtes un membre de www.AliExpress.com.    Pour ne plus recevoir nos emails promotionnels, Cliquez ici    Lisez notre Politique de confidentialité et conditions d'utilisation si vous avez des questions.    Centre de service clientèle AliExpress    Alibaba.com Singapore E-Commerce Private Limited,     c/o 26/F Tower One, Times Square, 1 Matheson Street, Causeway Bay, Hong Kong</t>
-  </si>
-  <si>
-    <t>LinkedIn &lt;updates-noreply@linkedin.com&gt;
-Jobs.tn shared a post: _x000D_
-LIKE EMPATHY APPRECIATION 4_x000D_
-_x000D_
-_x000D_
-Read more: https://www.linkedin.com/comm/feed/update/urn:li:activity:7440657250412703744?origin=NETWORK_CONVERSATIONS&amp;lipi=urn%3Ali%3Apage%3Aemail_email_network_conversations_01%3BCfZIpKdRR0mvHBQz3ppeXg%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=3lpwsiI46kfYc1&amp;trk=eml-email_network_conversations_01-network~post~cta~text-0-read~more&amp;trkEmail=eml-email_network_conversations_01-network~post~cta~text-0-read~more-null-m8w88x~mn4z61hs~sp-null-null&amp;eid=m8w88x-mn4z61hs-sp&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWUzYjc4N2NlZDc0NTk4YWQ4ZTY5N2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NzdlOWRlYzc0MzkyZjVhNjQ5NzUzMDEyNDQ4NDM5OGQ2ODNkOThhZjk4MDFhNzQxLDEsMQ%3D%3D_x000D_
-        _x000D_
-_x000D_
-_x000D_
-See more on LinkedIn: https://www.linkedin.com/comm/feed/?lipi=urn%3Ali%3Apage%3Aemail_email_network_conversations_01%3BCfZIpKdRR0mvHBQz3ppeXg%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=3lpwsiI46kfYc1&amp;trk=eml-email_network_conversations_01-footer_promo-0-footer_see_all&amp;trkEmail=eml-email_network_conversations_01-footer_promo-0-footer_see_all-null-m8w88x~mn4z61hs~sp-null-null&amp;eid=m8w88x-mn4z61hs-sp&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWUzYjc4N2NlZDc0NTk4YWQ4ZTY5N2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NzdlOWRlYzc0MzkyZjVhNjQ5NzUzMDEyNDQ4NDM5OGQ2ODNkOThhZjk4MDFhNzQxLDEsMQ%3D%3D_x000D_
-_x000D_
-----------------------------------------_x000D_
-_x000D_
-This email was intended for Yessine Hadj Taieb (IT Student)_x000D_
-Learn why we included this: https://www.linkedin.com/help/linkedin/answer/4788?lang=en&amp;lipi=urn%3Ali%3Apage%3Aemail_email_network_conversations_01%3BCfZIpKdRR0mvHBQz3ppeXg%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=3lpwsiI46kfYc1&amp;trk=eml-email_network_conversations_01-SecurityHelp-0-textfooterglimmer&amp;trkEmail=eml-email_network_conversations_01-SecurityHelp-0-textfooterglimmer-null-m8w88x~mn4z61hs~sp-null-null&amp;eid=m8w88x-mn4z61hs-sp&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWUzYjc4N2NlZDc0NTk4YWQ4ZTY5N2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NzdlOWRlYzc0MzkyZjVhNjQ5NzUzMDEyNDQ4NDM5OGQ2ODNkOThhZjk4MDFhNzQxLDEsMQ%3D%3D_x000D_
-You are receiving Network Conversations emails. Some content may be automatically translated based on_x000D_
-      &lt;a href="https://www.linkedin.com/mypreferences/d/language-for-translation" target="_blank" class="link-no-visited-state" data-tracking-will-navigate data-tracking-control-name="email_network_conversations_content_settings_link" style="cursor: pointer; display: inline-block; text-decoration: none; -webkit-text-size-adjust: 100%; -ms-text-size-adjust: 100%; font-weight: 600; color: #0a66c2;"&gt;your settings&lt;/a&gt;._x000D_
-_x000D_
-_x000D_
-Unsubscribe: https://www.linkedin.com/comm/mypreferences/u/emailunsub?action=updateEmailSubscription&amp;lipi=urn%3Ali%3Apage%3Aemail_email_network_conversations_01%3BCfZIpKdRR0mvHBQz3ppeXg%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=3lpwsiI46kfYc1&amp;trk=eml-email_network_conversations_01-unsubscribe-0-textfooterglimmer&amp;trkEmail=eml-email_network_conversations_01-unsubscribe-0-textfooterglimmer-null-m8w88x~mn4z61hs~sp-null-null&amp;eid=m8w88x-mn4z61hs-sp&amp;loid=AQHzMFVHfHIsLwAAAZ0hVXKqfCmyRNYSGz-IlsovQben1M_TPBtOikJ5Tx3BbppQKyZ349yZEEXggz8Y17ZQ1EaPWsfLVzVBy55iEWqbqhyht5sTXMX0DcBULQ_x000D_
-Help: https://www.linkedin.com/help/linkedin/answer/67?lang=en&amp;lipi=urn%3Ali%3Apage%3Aemail_email_network_conversations_01%3BCfZIpKdRR0mvHBQz3ppeXg%3D%3D&amp;midToken=AQFDdUEz6WQ9Uw&amp;midSig=3lpwsiI46kfYc1&amp;trk=eml-email_network_conversations_01-help-0-textfooterglimmer&amp;trkEmail=eml-email_network_conversations_01-help-0-textfooterglimmer-null-m8w88x~mn4z61hs~sp-null-null&amp;eid=m8w88x-mn4z61hs-sp&amp;otpToken=MTMwNjFhZTUxMzI3Y2ZjMGJjMmYwZmViNDExOWUzYjc4N2NlZDc0NTk4YWQ4ZTY5N2JjZTAxNjg0OTVkNThmYmYyZDJkMGU5NzdlOWRlYzc0MzkyZjVhNjQ5NzUzMDEyNDQ4NDM5OGQ2ODNkOThhZjk4MDFhNzQxLDEsMQ%3D%3D_x000D_
-_x000D_
-© 2026 LinkedIn Corporation, 1zwnj000 West Maude Avenue, Sunnyvale, CA 94085._x000D_
-LinkedIn and the LinkedIn logo are registered trademarks of LinkedIn.</t>
+this is a test for the attatchement</t>
+  </si>
+  <si>
+    <t>Rapport.pdf; Asset 11.png</t>
   </si>
 </sst>
 </file>
@@ -644,7 +370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -663,79 +389,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="C2" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
